--- a/MouleSmile_Carte_Admin.xlsx
+++ b/MouleSmile_Carte_Admin.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export Firebase" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boissons Menu" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desserts Menu" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu Enfant" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -27,7 +28,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00&quot; €&quot;"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -240,8 +241,21 @@
       <color rgb="00888888"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="FFAAAAAA"/>
+    </font>
+    <font>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="FF1A7A50"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="16">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -326,6 +340,26 @@
         <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E7"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -404,7 +438,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -608,6 +642,25 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="18" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="50" customWidth="1" style="29" min="1" max="1"/>
@@ -1106,6 +1159,18 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="69" t="inlineStr">
+        <is>
+          <t>Menu Enfant</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>Choix proposé au client après confirmation d'âge (Enfant 0-5 ans gratuit)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
@@ -1114,6 +1179,208 @@
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="30" min="1" max="1"/>
+    <col width="28" customWidth="1" style="30" min="2" max="2"/>
+    <col width="30" customWidth="1" style="30" min="3" max="3"/>
+    <col width="8" customWidth="1" style="30" min="4" max="4"/>
+    <col width="22" customWidth="1" style="30" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="30">
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>MENU ENFANT — CHOIX PROPOSÉ APRÈS CONFIRMATION D'ÂGE (0-5 ANS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" s="30">
+      <c r="A2" s="59" t="inlineStr">
+        <is>
+          <t>OUI = proposé dans le popup menu enfant | NON = non disponible pour le menu enfant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1" s="30">
+      <c r="A3" s="60" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B3" s="60" t="inlineStr">
+        <is>
+          <t>Nom</t>
+        </is>
+      </c>
+      <c r="C3" s="60" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D3" s="60" t="inlineStr">
+        <is>
+          <t>Emoji</t>
+        </is>
+      </c>
+      <c r="E3" s="60" t="inlineStr">
+        <is>
+          <t>Dans menu enfant (OUI/NON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" s="30">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>me1</t>
+        </is>
+      </c>
+      <c r="B4" s="71" t="inlineStr">
+        <is>
+          <t>Mini moules-frites</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
+        <is>
+          <t>Portion enfant adaptée + frites</t>
+        </is>
+      </c>
+      <c r="D4" s="72" t="inlineStr">
+        <is>
+          <t>🐚</t>
+        </is>
+      </c>
+      <c r="E4" s="73" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" s="30">
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>me2</t>
+        </is>
+      </c>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>Nuggets &amp; frites</t>
+        </is>
+      </c>
+      <c r="C5" s="74" t="inlineStr">
+        <is>
+          <t>5 nuggets maison + frites</t>
+        </is>
+      </c>
+      <c r="D5" s="75" t="inlineStr">
+        <is>
+          <t>🍗</t>
+        </is>
+      </c>
+      <c r="E5" s="73" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" s="30">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>me3</t>
+        </is>
+      </c>
+      <c r="B6" s="71" t="inlineStr">
+        <is>
+          <t>Steak haché &amp; frites</t>
+        </is>
+      </c>
+      <c r="C6" s="71" t="inlineStr">
+        <is>
+          <t>Steak haché + frites fraîches</t>
+        </is>
+      </c>
+      <c r="D6" s="72" t="inlineStr">
+        <is>
+          <t>🍔</t>
+        </is>
+      </c>
+      <c r="E6" s="73" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1" s="30">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>me4</t>
+        </is>
+      </c>
+      <c r="B7" s="74" t="inlineStr">
+        <is>
+          <t>Glace enfant</t>
+        </is>
+      </c>
+      <c r="C7" s="74" t="inlineStr">
+        <is>
+          <t>1 boule au choix</t>
+        </is>
+      </c>
+      <c r="D7" s="75" t="inlineStr">
+        <is>
+          <t>🍦</t>
+        </is>
+      </c>
+      <c r="E7" s="73" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1" s="30">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>me5</t>
+        </is>
+      </c>
+      <c r="B8" s="71" t="inlineStr">
+        <is>
+          <t>Sirop à l'eau</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="inlineStr">
+        <is>
+          <t>Fraise, menthe ou grenadine</t>
+        </is>
+      </c>
+      <c r="D8" s="72" t="inlineStr">
+        <is>
+          <t>🧃</t>
+        </is>
+      </c>
+      <c r="E8" s="73" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A10:E10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3032,8 +3299,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A38:G38"/>
     <mergeCell ref="A42:G42"/>
     <mergeCell ref="A33:G33"/>

--- a/MouleSmile_Carte_Admin.xlsx
+++ b/MouleSmile_Carte_Admin.xlsx
@@ -16,6 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boissons Menu" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Desserts Menu" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Menu Enfant" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Familles Options" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Options Produits" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -903,6 +905,620 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>FAMILLES D'OPTIONS RÉUTILISABLES (coulis, croquant, nappage...)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Une famille = un groupe de choix. Assignez ensuite une famille à un produit dans l'onglet 'Options Produits'.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID Famille</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Nom Famille</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>ID Option</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Nom Option</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Supplément (EUR)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Actif (OUI/NON)</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Ordre</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>coulis</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Coulis</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>co1</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Chocolat</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>coulis</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Coulis</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>co2</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Caramel</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>coulis</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Coulis</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>co3</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>Fruit rouge</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>croquant</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Croquant</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>cr1</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>M&amp;M's</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>croquant</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Croquant</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>cr2</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Daim</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>croquant</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Croquant</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>cr3</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Sans croquant</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>nappage_crepe</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Nappage crêpe/gaufre</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>na1</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>nappage_crepe</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Nappage crêpe/gaufre</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>na2</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>nappage_crepe</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Nappage crêpe/gaufre</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>na3</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Coulis chocolat</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>nappage_crepe</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Nappage crêpe/gaufre</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>na4</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Coulis caramel</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>💡 ID Famille identique sur plusieurs lignes = les options d'une même famille (ex: coulis)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>💡 Créez une nouvelle famille en inventant un nouvel ID Famille (ex: 'sauce_burger')</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ASSIGNATION DES OPTIONS AUX PRODUITS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Associez un ID Produit (colonne A des onglets Formules/Desserts/etc.) à une Famille d'Options. Étape = ordre d'affichage des popups (1, 2, 3...).</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>ID Produit</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Nom Produit (repère)</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>ID Famille</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Étape (ordre)</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Actif (OUI/NON)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>d4</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Crêpe</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>nappage_crepe</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>d5</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Gaufre</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>nappage_crepe</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>d6</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Sundae</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>coulis</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>d6</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Sundae</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>croquant</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>💡 Le Sundae a 2 lignes : coulis (étape 1) puis croquant (étape 2) → 2 popups successifs</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>💡 Pour un produit sans option, ne créez simplement aucune ligne pour son ID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3133,7 +3749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3341,8 +3957,125 @@
         <v>3</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>d4</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>desserts</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr"/>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Crêpe</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Choisissez votre nappage</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>🥞</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>4</v>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>d5</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>desserts</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr"/>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Gaufre</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>Choisissez votre nappage</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>🧇</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>d6</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>desserts</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr"/>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Sundae</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Glace vanille — choisissez coulis et croquant</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>🍨</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>OUI</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  ↓ Ajoutez vos produits ici en suivant le même format</t>
         </is>

--- a/MouleSmile_Carte_Admin.xlsx
+++ b/MouleSmile_Carte_Admin.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="845" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="409">
   <si>
     <t>MOULE &amp; SMILE — GESTION DE CARTE</t>
   </si>
@@ -258,6 +258,12 @@
     <t>6 nuggets + frites maison</t>
   </si>
   <si>
+    <t>6 nuggets  + frites fraîches</t>
+  </si>
+  <si>
+    <t>🍗</t>
+  </si>
+  <si>
     <t>en1</t>
   </si>
   <si>
@@ -366,6 +372,15 @@
     <t>🌞</t>
   </si>
   <si>
+    <t>s7</t>
+  </si>
+  <si>
+    <t>Safran</t>
+  </si>
+  <si>
+    <t>créme fraiche, infusion de safran</t>
+  </si>
+  <si>
     <t>MOULE &amp; SMILE — BOISSONS</t>
   </si>
   <si>
@@ -375,769 +390,841 @@
     <t xml:space="preserve">  — Softs —</t>
   </si>
   <si>
+    <t>b3</t>
+  </si>
+  <si>
+    <t>softs</t>
+  </si>
+  <si>
+    <t>Coca-Cola</t>
+  </si>
+  <si>
+    <t>33cl</t>
+  </si>
+  <si>
+    <t>🥤</t>
+  </si>
+  <si>
+    <t>b4</t>
+  </si>
+  <si>
+    <t>Orangina</t>
+  </si>
+  <si>
+    <t>🍊</t>
+  </si>
+  <si>
+    <t>b6</t>
+  </si>
+  <si>
+    <t>Limonade</t>
+  </si>
+  <si>
+    <t>🍋</t>
+  </si>
+  <si>
     <t>b1</t>
   </si>
   <si>
-    <t>softs</t>
-  </si>
-  <si>
-    <t>Coca-Cola</t>
-  </si>
-  <si>
-    <t>33cl</t>
-  </si>
-  <si>
-    <t>🥤</t>
+    <t>Eau plate</t>
+  </si>
+  <si>
+    <t>50cl</t>
+  </si>
+  <si>
+    <t>💧</t>
   </si>
   <si>
     <t>b2</t>
   </si>
   <si>
-    <t>Orangina</t>
-  </si>
-  <si>
-    <t>🍊</t>
-  </si>
-  <si>
-    <t>b3</t>
-  </si>
-  <si>
-    <t>Limonade</t>
-  </si>
-  <si>
-    <t>🍋</t>
-  </si>
-  <si>
-    <t>b4</t>
-  </si>
-  <si>
-    <t>Eau plate</t>
-  </si>
-  <si>
-    <t>50cl</t>
-  </si>
-  <si>
-    <t>💧</t>
+    <t>Eau gazeuse</t>
+  </si>
+  <si>
+    <t>b35</t>
+  </si>
+  <si>
+    <t>Jus de fruits préssé</t>
+  </si>
+  <si>
+    <t>25cl</t>
+  </si>
+  <si>
+    <t>🍹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — Bières —</t>
+  </si>
+  <si>
+    <t>b7</t>
+  </si>
+  <si>
+    <t>bieres</t>
+  </si>
+  <si>
+    <t>Bière pression</t>
+  </si>
+  <si>
+    <t>🍺</t>
+  </si>
+  <si>
+    <t>b8</t>
+  </si>
+  <si>
+    <t>b9</t>
+  </si>
+  <si>
+    <t>Bière bouteille</t>
+  </si>
+  <si>
+    <t>b10</t>
+  </si>
+  <si>
+    <t>Bière sans alcool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — Vins Blancs —</t>
+  </si>
+  <si>
+    <t>b11</t>
+  </si>
+  <si>
+    <t>vins</t>
+  </si>
+  <si>
+    <t>Blanc</t>
+  </si>
+  <si>
+    <t>Picpoul de Pinet AOP</t>
+  </si>
+  <si>
+    <t>Codet 25cl</t>
+  </si>
+  <si>
+    <t>🥂</t>
+  </si>
+  <si>
+    <t>b12</t>
+  </si>
+  <si>
+    <t>Pichet 50cl</t>
+  </si>
+  <si>
+    <t>b13</t>
+  </si>
+  <si>
+    <t>Bouteille 75cl</t>
+  </si>
+  <si>
+    <t>b14</t>
+  </si>
+  <si>
+    <t>La Clape Blanc AOP</t>
+  </si>
+  <si>
+    <t>b15</t>
+  </si>
+  <si>
+    <t>Gérard Bertrand Blanc</t>
+  </si>
+  <si>
+    <t>b16</t>
+  </si>
+  <si>
+    <t>Magnum 1,5L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — Vins Rosés —</t>
+  </si>
+  <si>
+    <t>b17</t>
+  </si>
+  <si>
+    <t>Rosé</t>
+  </si>
+  <si>
+    <t>Corbières Rosé AOP</t>
+  </si>
+  <si>
+    <t>🍷</t>
+  </si>
+  <si>
+    <t>b18</t>
+  </si>
+  <si>
+    <t>b19</t>
+  </si>
+  <si>
+    <t>b20</t>
+  </si>
+  <si>
+    <t>La Clape Rosé AOP</t>
+  </si>
+  <si>
+    <t>b21</t>
+  </si>
+  <si>
+    <t>Gérard Bertrand Rosé</t>
+  </si>
+  <si>
+    <t>b22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — Vins Rouges —</t>
+  </si>
+  <si>
+    <t>b23</t>
+  </si>
+  <si>
+    <t>Rouge</t>
+  </si>
+  <si>
+    <t>Minervois Rouge AOP</t>
+  </si>
+  <si>
+    <t>b24</t>
+  </si>
+  <si>
+    <t>Corbières Rouge AOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — Cocktails &amp; Sangria —</t>
+  </si>
+  <si>
+    <t>b25</t>
+  </si>
+  <si>
+    <t>cocktails</t>
+  </si>
+  <si>
+    <t>Cocktails</t>
+  </si>
+  <si>
+    <t>Spritz</t>
+  </si>
+  <si>
+    <t>Aperol, Prosecco, eau gazeuse — 25cl</t>
+  </si>
+  <si>
+    <t>b26</t>
+  </si>
+  <si>
+    <t>Mojito</t>
+  </si>
+  <si>
+    <t>Rhum, menthe fraîche, citron vert — 25cl</t>
+  </si>
+  <si>
+    <t>b27</t>
+  </si>
+  <si>
+    <t>Moscow Mule</t>
+  </si>
+  <si>
+    <t>Vodka, ginger beer, citron — 25cl</t>
+  </si>
+  <si>
+    <t>b28</t>
+  </si>
+  <si>
+    <t>Pastis / Ricard</t>
+  </si>
+  <si>
+    <t>4cl</t>
+  </si>
+  <si>
+    <t>🥃</t>
+  </si>
+  <si>
+    <t>b29</t>
+  </si>
+  <si>
+    <t>Sangria</t>
+  </si>
+  <si>
+    <t>Sangria Maison</t>
+  </si>
+  <si>
+    <t>Verre 25cl — Vin rouge Corbières, fruits frais</t>
+  </si>
+  <si>
+    <t>b30</t>
+  </si>
+  <si>
+    <t>b31</t>
+  </si>
+  <si>
+    <t>Pichet 1L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — Chauds —</t>
+  </si>
+  <si>
+    <t>b32</t>
+  </si>
+  <si>
+    <t>chauds</t>
+  </si>
+  <si>
+    <t>Café / Expresso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cafe noir </t>
+  </si>
+  <si>
+    <t>☕</t>
+  </si>
+  <si>
+    <t>b33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Café noisette </t>
+  </si>
+  <si>
+    <t xml:space="preserve">café accompagné de lait </t>
+  </si>
+  <si>
+    <t>b34</t>
+  </si>
+  <si>
+    <t>Thé / Infusion</t>
+  </si>
+  <si>
+    <t>🍵</t>
   </si>
   <si>
     <t>b5</t>
   </si>
   <si>
-    <t>Eau gazeuse</t>
-  </si>
-  <si>
-    <t>b6</t>
-  </si>
-  <si>
-    <t>Jus de fruits préssé</t>
-  </si>
-  <si>
-    <t>25cl</t>
-  </si>
-  <si>
-    <t>🍹</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  — Bières —</t>
-  </si>
-  <si>
-    <t>b7</t>
-  </si>
-  <si>
-    <t>bieres</t>
-  </si>
-  <si>
-    <t>Bière pression</t>
-  </si>
-  <si>
-    <t>🍺</t>
-  </si>
-  <si>
-    <t>b8</t>
-  </si>
-  <si>
-    <t>b9</t>
-  </si>
-  <si>
-    <t>Bière bouteille</t>
-  </si>
-  <si>
-    <t>b10</t>
-  </si>
-  <si>
-    <t>Bière sans alcool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  — Vins Blancs —</t>
-  </si>
-  <si>
-    <t>b11</t>
-  </si>
-  <si>
-    <t>vins</t>
-  </si>
-  <si>
-    <t>Blanc</t>
-  </si>
-  <si>
-    <t>Picpoul de Pinet AOP</t>
-  </si>
-  <si>
-    <t>Codet 25cl</t>
-  </si>
-  <si>
-    <t>🥂</t>
-  </si>
-  <si>
-    <t>b12</t>
-  </si>
-  <si>
-    <t>Pichet 50cl</t>
-  </si>
-  <si>
-    <t>b13</t>
-  </si>
-  <si>
-    <t>Bouteille 75cl</t>
-  </si>
-  <si>
-    <t>b14</t>
-  </si>
-  <si>
-    <t>La Clape Blanc AOP</t>
-  </si>
-  <si>
-    <t>b15</t>
-  </si>
-  <si>
-    <t>Gérard Bertrand Blanc</t>
-  </si>
-  <si>
-    <t>b16</t>
-  </si>
-  <si>
-    <t>Magnum 1,5L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  — Vins Rosés —</t>
-  </si>
-  <si>
-    <t>b17</t>
-  </si>
-  <si>
-    <t>Rosé</t>
-  </si>
-  <si>
-    <t>Corbières Rosé AOP</t>
-  </si>
-  <si>
-    <t>🍷</t>
-  </si>
-  <si>
-    <t>b18</t>
-  </si>
-  <si>
-    <t>b19</t>
-  </si>
-  <si>
-    <t>b20</t>
-  </si>
-  <si>
-    <t>La Clape Rosé AOP</t>
-  </si>
-  <si>
-    <t>b21</t>
-  </si>
-  <si>
-    <t>Gérard Bertrand Rosé</t>
-  </si>
-  <si>
-    <t>b22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  — Vins Rouges —</t>
-  </si>
-  <si>
-    <t>b23</t>
-  </si>
-  <si>
-    <t>Rouge</t>
-  </si>
-  <si>
-    <t>Minervois Rouge AOP</t>
-  </si>
-  <si>
-    <t>b24</t>
-  </si>
-  <si>
-    <t>Corbières Rouge AOP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  — Cocktails &amp; Sangria —</t>
-  </si>
-  <si>
-    <t>b25</t>
-  </si>
-  <si>
-    <t>cocktails</t>
-  </si>
-  <si>
-    <t>Cocktails</t>
-  </si>
-  <si>
-    <t>Spritz</t>
-  </si>
-  <si>
-    <t>Aperol, Prosecco, eau gazeuse — 25cl</t>
-  </si>
-  <si>
-    <t>b26</t>
-  </si>
-  <si>
-    <t>Mojito</t>
-  </si>
-  <si>
-    <t>Rhum, menthe fraîche, citron vert — 25cl</t>
-  </si>
-  <si>
-    <t>b27</t>
-  </si>
-  <si>
-    <t>Moscow Mule</t>
-  </si>
-  <si>
-    <t>Vodka, ginger beer, citron — 25cl</t>
-  </si>
-  <si>
-    <t>b28</t>
-  </si>
-  <si>
-    <t>Pastis / Ricard</t>
-  </si>
-  <si>
-    <t>4cl</t>
-  </si>
-  <si>
-    <t>🥃</t>
-  </si>
-  <si>
-    <t>b29</t>
-  </si>
-  <si>
-    <t>Sangria</t>
-  </si>
-  <si>
-    <t>Sangria Maison</t>
-  </si>
-  <si>
-    <t>Verre 25cl — Vin rouge Corbières, fruits frais</t>
-  </si>
-  <si>
-    <t>b30</t>
-  </si>
-  <si>
-    <t>b31</t>
-  </si>
-  <si>
-    <t>Pichet 1L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  — Chauds —</t>
-  </si>
-  <si>
-    <t>b32</t>
-  </si>
-  <si>
-    <t>chauds</t>
-  </si>
-  <si>
-    <t>Café / Expresso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cafe noir </t>
-  </si>
-  <si>
-    <t>☕</t>
-  </si>
-  <si>
-    <t>b33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Café noisette </t>
-  </si>
-  <si>
-    <t xml:space="preserve">café accompagné de lait </t>
-  </si>
-  <si>
-    <t>b34</t>
-  </si>
-  <si>
-    <t>Thé / Infusion</t>
-  </si>
-  <si>
-    <t>🍵</t>
-  </si>
-  <si>
-    <t>b35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">chewps agrume </t>
+    <t xml:space="preserve">Chewppes agrume </t>
+  </si>
+  <si>
+    <t xml:space="preserve">33 cl </t>
+  </si>
+  <si>
+    <t>b0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sirop à l'eau </t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 cl </t>
+  </si>
+  <si>
+    <t>b37</t>
+  </si>
+  <si>
+    <t>b38</t>
+  </si>
+  <si>
+    <t>b39</t>
+  </si>
+  <si>
+    <t>b40</t>
+  </si>
+  <si>
+    <t>MOULE &amp; SMILE — DESSERTS</t>
+  </si>
+  <si>
+    <t>⚡ Cellules en BLEU = modifiables</t>
+  </si>
+  <si>
+    <t>d1</t>
+  </si>
+  <si>
+    <t>desserts</t>
+  </si>
+  <si>
+    <t>Dessert du jour</t>
+  </si>
+  <si>
+    <t>Demandez à votre serveur</t>
+  </si>
+  <si>
+    <t>🍮</t>
+  </si>
+  <si>
+    <t>NON</t>
+  </si>
+  <si>
+    <t>d2</t>
+  </si>
+  <si>
+    <t>Glace italienne</t>
+  </si>
+  <si>
+    <t>Vanille ou chocolat</t>
+  </si>
+  <si>
+    <t>🍦</t>
+  </si>
+  <si>
+    <t>d3</t>
+  </si>
+  <si>
+    <t>Mousse au chocolat</t>
+  </si>
+  <si>
+    <t>Maison</t>
+  </si>
+  <si>
+    <t>🍫</t>
+  </si>
+  <si>
+    <t>d4</t>
+  </si>
+  <si>
+    <t>Crêpe</t>
+  </si>
+  <si>
+    <t>Choisissez votre nappage</t>
+  </si>
+  <si>
+    <t>🥞</t>
+  </si>
+  <si>
+    <t>d5</t>
+  </si>
+  <si>
+    <t>Gaufre</t>
+  </si>
+  <si>
+    <t>🧇</t>
+  </si>
+  <si>
+    <t>d6</t>
+  </si>
+  <si>
+    <t>Sundae</t>
+  </si>
+  <si>
+    <t>Glace vanille — choisissez coulis et croquant</t>
+  </si>
+  <si>
+    <t>🍨</t>
+  </si>
+  <si>
+    <t>MOULE &amp; SMILE — DIGESTIFS</t>
+  </si>
+  <si>
+    <t>dg1</t>
+  </si>
+  <si>
+    <t>digestifs</t>
+  </si>
+  <si>
+    <t>Cabanel</t>
+  </si>
+  <si>
+    <t>Liqueur artisanale Carcassonne — 4cl</t>
+  </si>
+  <si>
+    <t>🍋🌿🍊</t>
+  </si>
+  <si>
+    <t>dg2</t>
+  </si>
+  <si>
+    <t>Cognac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eau-de-vie de vin prestigieuse de Charente - 4cl </t>
+  </si>
+  <si>
+    <t>dg3</t>
+  </si>
+  <si>
+    <t>Armagnac</t>
+  </si>
+  <si>
+    <t>Plus ancienne eau-de-vie de vin de Gascogne - 4cl</t>
+  </si>
+  <si>
+    <t>BOISSONS PROPOSÉES GRATUITEMENT DANS CERTAINS POPUPS SPÉCIAUX</t>
+  </si>
+  <si>
+    <t>OUI = boisson proposée gratuitement | NON = non disponible dans ce menu (reste sur la carte payante)</t>
+  </si>
+  <si>
+    <t>bm1</t>
+  </si>
+  <si>
+    <t>bm2</t>
+  </si>
+  <si>
+    <t>bm3</t>
+  </si>
+  <si>
+    <t>bm4</t>
+  </si>
+  <si>
+    <t>bm5</t>
+  </si>
+  <si>
+    <t>bm6</t>
+  </si>
+  <si>
+    <t>Jus de fruits</t>
+  </si>
+  <si>
+    <t>bm7</t>
+  </si>
+  <si>
+    <t>bm8</t>
+  </si>
+  <si>
+    <t>50cl — supplément conseillé</t>
+  </si>
+  <si>
+    <t>bm9</t>
+  </si>
+  <si>
+    <t>Verre de vin rosé</t>
+  </si>
+  <si>
+    <t>Codet 25cl — Corbières Rosé AOP</t>
+  </si>
+  <si>
+    <t>bm10</t>
+  </si>
+  <si>
+    <t>Verre de vin blanc</t>
+  </si>
+  <si>
+    <t>Codet 25cl — Picpoul de Pinet AOP</t>
+  </si>
+  <si>
+    <t>bm11</t>
+  </si>
+  <si>
+    <t>Verre de vin rouge</t>
+  </si>
+  <si>
+    <t>Bouteille 75cl — Minervois</t>
+  </si>
+  <si>
+    <t>bm12</t>
+  </si>
+  <si>
+    <t>25cl — supplément conseillé</t>
+  </si>
+  <si>
+    <t>bm13</t>
+  </si>
+  <si>
+    <t>💡 Ajoutez autant de boissons que vous souhaitez</t>
+  </si>
+  <si>
+    <t>DESSERTS PROPOSÉS DANS LE POPUP AVANT ADDITION</t>
+  </si>
+  <si>
+    <t>OUI = proposé dans le popup dessert/café avant l'addition (avec compteur +/-) | NON = non proposé</t>
+  </si>
+  <si>
+    <t>dm1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dessert </t>
+  </si>
+  <si>
+    <t>dm2</t>
+  </si>
+  <si>
+    <t>dm3</t>
+  </si>
+  <si>
+    <t>dm4</t>
+  </si>
+  <si>
+    <t>Tarte du jour</t>
+  </si>
+  <si>
+    <t>Selon arrivage</t>
+  </si>
+  <si>
+    <t>🥧</t>
+  </si>
+  <si>
+    <t>dm5</t>
+  </si>
+  <si>
+    <t>Crème brûlée</t>
+  </si>
+  <si>
+    <t>Maison — sur réservation</t>
+  </si>
+  <si>
+    <t>💡 Le popup propose aussi automatiquement les boissons chaudes (catégorie Chauds)</t>
+  </si>
+  <si>
+    <t>MENU ENFANT — CHOIX PROPOSÉ APRÈS CONFIRMATION D'ÂGE (0-5 ANS)</t>
+  </si>
+  <si>
+    <t>OUI = proposé dans le popup menu enfant | NON = non disponible pour le menu enfant</t>
+  </si>
+  <si>
+    <t>me1</t>
+  </si>
+  <si>
+    <t>Mini moules-frites</t>
+  </si>
+  <si>
+    <t>Portion enfant adaptée + frites</t>
+  </si>
+  <si>
+    <t>me2</t>
+  </si>
+  <si>
+    <t>Nuggets &amp; frites</t>
+  </si>
+  <si>
+    <t>4 nuggets maison + frites</t>
+  </si>
+  <si>
+    <t>me3</t>
+  </si>
+  <si>
+    <t>Steak haché &amp; frites</t>
+  </si>
+  <si>
+    <t>Steak haché + frites fraîches</t>
+  </si>
+  <si>
+    <t>🍔</t>
+  </si>
+  <si>
+    <t>me4</t>
+  </si>
+  <si>
+    <t>Glace enfant</t>
+  </si>
+  <si>
+    <t>1 boule au choix</t>
+  </si>
+  <si>
+    <t>me5</t>
+  </si>
+  <si>
+    <t>Sirop à l'eau</t>
+  </si>
+  <si>
+    <t>Fraise, menthe ou grenadine</t>
+  </si>
+  <si>
+    <t>🧃</t>
+  </si>
+  <si>
+    <t>💡 Ajoutez autant de plats enfant que vous souhaitez</t>
+  </si>
+  <si>
+    <t>FAMILLES D'OPTIONS RÉUTILISABLES (coulis, croquant, nappage...)</t>
+  </si>
+  <si>
+    <t>Une famille = un groupe de choix. Assignez ensuite une famille à un produit dans l'onglet 'Options Produits'.</t>
+  </si>
+  <si>
+    <t>ID Famille</t>
+  </si>
+  <si>
+    <t>Nom Famille</t>
+  </si>
+  <si>
+    <t>ID Option</t>
+  </si>
+  <si>
+    <t>Nom Option</t>
+  </si>
+  <si>
+    <t>Supplément (EUR)</t>
+  </si>
+  <si>
+    <t>coulis</t>
+  </si>
+  <si>
+    <t>Coulis</t>
+  </si>
+  <si>
+    <t>co1</t>
+  </si>
+  <si>
+    <t>Chocolat</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>Caramel</t>
+  </si>
+  <si>
+    <t>co3</t>
+  </si>
+  <si>
+    <t>Fruit rouge</t>
+  </si>
+  <si>
+    <t>co4</t>
+  </si>
+  <si>
+    <t>co5</t>
+  </si>
+  <si>
+    <t>croquant</t>
+  </si>
+  <si>
+    <t>Croquant</t>
+  </si>
+  <si>
+    <t>cr1</t>
+  </si>
+  <si>
+    <t>M&amp;M's</t>
+  </si>
+  <si>
+    <t>cr2</t>
+  </si>
+  <si>
+    <t>Daim</t>
+  </si>
+  <si>
+    <t>cr3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speculos </t>
+  </si>
+  <si>
+    <t>cr4</t>
+  </si>
+  <si>
+    <t>Sans croquant</t>
+  </si>
+  <si>
+    <t>cr5</t>
+  </si>
+  <si>
+    <t>nappage_crepe</t>
+  </si>
+  <si>
+    <t>Nappage</t>
+  </si>
+  <si>
+    <t>na1</t>
+  </si>
+  <si>
+    <t>Sucre</t>
+  </si>
+  <si>
+    <t>na2</t>
+  </si>
+  <si>
+    <t>Nature</t>
+  </si>
+  <si>
+    <t>na3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Citron frais </t>
+  </si>
+  <si>
+    <t>na4</t>
+  </si>
+  <si>
+    <t>Coulis chocolat</t>
+  </si>
+  <si>
+    <t>na5</t>
+  </si>
+  <si>
+    <t>Coulis caramel</t>
+  </si>
+  <si>
+    <t>na6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glace vanille </t>
+  </si>
+  <si>
+    <t>sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sauce </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mariniére </t>
+  </si>
+  <si>
+    <t>Rocquefort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curry </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créme-échalote </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomate Chorizo </t>
+  </si>
+  <si>
+    <t>s0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pas de sauce </t>
+  </si>
+  <si>
+    <t>gout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digestif </t>
+  </si>
+  <si>
+    <t>Citron</t>
+  </si>
+  <si>
+    <t>Menthe</t>
+  </si>
+  <si>
+    <t>Clementine</t>
+  </si>
+  <si>
+    <t>sirop</t>
+  </si>
+  <si>
+    <t>Soft</t>
   </si>
   <si>
     <t>b36</t>
   </si>
   <si>
-    <t>b37</t>
-  </si>
-  <si>
-    <t>b38</t>
-  </si>
-  <si>
-    <t>b39</t>
-  </si>
-  <si>
-    <t>b40</t>
-  </si>
-  <si>
-    <t>MOULE &amp; SMILE — DESSERTS</t>
-  </si>
-  <si>
-    <t>⚡ Cellules en BLEU = modifiables</t>
-  </si>
-  <si>
-    <t>d1</t>
-  </si>
-  <si>
-    <t>desserts</t>
-  </si>
-  <si>
-    <t>Dessert du jour</t>
-  </si>
-  <si>
-    <t>Demandez à votre serveur</t>
-  </si>
-  <si>
-    <t>🍮</t>
-  </si>
-  <si>
-    <t>d2</t>
-  </si>
-  <si>
-    <t>Glace italienne</t>
-  </si>
-  <si>
-    <t>Vanille ou chocolat</t>
-  </si>
-  <si>
-    <t>🍦</t>
-  </si>
-  <si>
-    <t>d3</t>
-  </si>
-  <si>
-    <t>Mousse au chocolat</t>
-  </si>
-  <si>
-    <t>Maison</t>
-  </si>
-  <si>
-    <t>🍫</t>
-  </si>
-  <si>
-    <t>d4</t>
-  </si>
-  <si>
-    <t>Crêpe</t>
-  </si>
-  <si>
-    <t>Choisissez votre nappage</t>
-  </si>
-  <si>
-    <t>🥞</t>
-  </si>
-  <si>
-    <t>d5</t>
-  </si>
-  <si>
-    <t>Gaufre</t>
-  </si>
-  <si>
-    <t>🧇</t>
-  </si>
-  <si>
-    <t>d6</t>
-  </si>
-  <si>
-    <t>Sundae</t>
-  </si>
-  <si>
-    <t>Glace vanille — choisissez coulis et croquant</t>
-  </si>
-  <si>
-    <t>🍨</t>
-  </si>
-  <si>
-    <t>MOULE &amp; SMILE — DIGESTIFS</t>
-  </si>
-  <si>
-    <t>dg1</t>
-  </si>
-  <si>
-    <t>digestifs</t>
-  </si>
-  <si>
-    <t>Cabanel Citron</t>
-  </si>
-  <si>
-    <t>Liqueur artisanale Carcassonne — 4cl</t>
-  </si>
-  <si>
-    <t>dg2</t>
-  </si>
-  <si>
-    <t>Cabanel Menthe</t>
-  </si>
-  <si>
-    <t>dg3</t>
-  </si>
-  <si>
-    <t>Cabanel Clémentine</t>
-  </si>
-  <si>
-    <t>BOISSONS PROPOSÉES GRATUITEMENT DANS CERTAINS POPUPS SPÉCIAUX</t>
-  </si>
-  <si>
-    <t>OUI = boisson proposée gratuitement | NON = non disponible dans ce menu (reste sur la carte payante)</t>
-  </si>
-  <si>
-    <t>bm1</t>
-  </si>
-  <si>
-    <t>bm2</t>
-  </si>
-  <si>
-    <t>bm3</t>
-  </si>
-  <si>
-    <t>bm4</t>
-  </si>
-  <si>
-    <t>bm5</t>
-  </si>
-  <si>
-    <t>bm6</t>
-  </si>
-  <si>
-    <t>Jus de fruits</t>
-  </si>
-  <si>
-    <t>bm7</t>
-  </si>
-  <si>
-    <t>bm8</t>
-  </si>
-  <si>
-    <t>50cl — supplément conseillé</t>
-  </si>
-  <si>
-    <t>NON</t>
-  </si>
-  <si>
-    <t>bm9</t>
-  </si>
-  <si>
-    <t>Verre de vin rosé</t>
-  </si>
-  <si>
-    <t>Codet 25cl — Corbières Rosé AOP</t>
-  </si>
-  <si>
-    <t>bm10</t>
-  </si>
-  <si>
-    <t>Verre de vin blanc</t>
-  </si>
-  <si>
-    <t>Codet 25cl — Picpoul de Pinet AOP</t>
-  </si>
-  <si>
-    <t>bm11</t>
-  </si>
-  <si>
-    <t>Verre de vin rouge</t>
-  </si>
-  <si>
-    <t>Bouteille 75cl — Minervois</t>
-  </si>
-  <si>
-    <t>bm12</t>
-  </si>
-  <si>
-    <t>25cl — supplément conseillé</t>
-  </si>
-  <si>
-    <t>bm13</t>
-  </si>
-  <si>
-    <t>💡 Ajoutez autant de boissons que vous souhaitez</t>
-  </si>
-  <si>
-    <t>DESSERTS PROPOSÉS DANS LE POPUP AVANT ADDITION</t>
-  </si>
-  <si>
-    <t>OUI = proposé dans le popup dessert/café avant l'addition (avec compteur +/-) | NON = non proposé</t>
-  </si>
-  <si>
-    <t>dm1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dessert </t>
-  </si>
-  <si>
-    <t>dm2</t>
-  </si>
-  <si>
-    <t>dm3</t>
-  </si>
-  <si>
-    <t>dm4</t>
-  </si>
-  <si>
-    <t>Tarte du jour</t>
-  </si>
-  <si>
-    <t>Selon arrivage</t>
-  </si>
-  <si>
-    <t>🥧</t>
-  </si>
-  <si>
-    <t>dm5</t>
-  </si>
-  <si>
-    <t>Crème brûlée</t>
-  </si>
-  <si>
-    <t>Maison — sur réservation</t>
-  </si>
-  <si>
-    <t>💡 Le popup propose aussi automatiquement les boissons chaudes (catégorie Chauds)</t>
-  </si>
-  <si>
-    <t>MENU ENFANT — CHOIX PROPOSÉ APRÈS CONFIRMATION D'ÂGE (0-5 ANS)</t>
-  </si>
-  <si>
-    <t>OUI = proposé dans le popup menu enfant | NON = non disponible pour le menu enfant</t>
-  </si>
-  <si>
-    <t>me1</t>
-  </si>
-  <si>
-    <t>Mini moules-frites</t>
-  </si>
-  <si>
-    <t>Portion enfant adaptée + frites</t>
-  </si>
-  <si>
-    <t>me2</t>
-  </si>
-  <si>
-    <t>Nuggets &amp; frites</t>
-  </si>
-  <si>
-    <t>5 nuggets maison + frites</t>
-  </si>
-  <si>
-    <t>🍗</t>
-  </si>
-  <si>
-    <t>me3</t>
-  </si>
-  <si>
-    <t>Steak haché &amp; frites</t>
-  </si>
-  <si>
-    <t>Steak haché + frites fraîches</t>
-  </si>
-  <si>
-    <t>🍔</t>
-  </si>
-  <si>
-    <t>me4</t>
-  </si>
-  <si>
-    <t>Glace enfant</t>
-  </si>
-  <si>
-    <t>1 boule au choix</t>
-  </si>
-  <si>
-    <t>me5</t>
-  </si>
-  <si>
-    <t>Sirop à l'eau</t>
-  </si>
-  <si>
-    <t>Fraise, menthe ou grenadine</t>
-  </si>
-  <si>
-    <t>🧃</t>
-  </si>
-  <si>
-    <t>💡 Ajoutez autant de plats enfant que vous souhaitez</t>
-  </si>
-  <si>
-    <t>FAMILLES D'OPTIONS RÉUTILISABLES (coulis, croquant, nappage...)</t>
-  </si>
-  <si>
-    <t>Une famille = un groupe de choix. Assignez ensuite une famille à un produit dans l'onglet 'Options Produits'.</t>
-  </si>
-  <si>
-    <t>ID Famille</t>
-  </si>
-  <si>
-    <t>Nom Famille</t>
-  </si>
-  <si>
-    <t>ID Option</t>
-  </si>
-  <si>
-    <t>Nom Option</t>
-  </si>
-  <si>
-    <t>Supplément (EUR)</t>
-  </si>
-  <si>
-    <t>coulis</t>
-  </si>
-  <si>
-    <t>Coulis</t>
-  </si>
-  <si>
-    <t>co1</t>
-  </si>
-  <si>
-    <t>Chocolat</t>
-  </si>
-  <si>
-    <t>co2</t>
-  </si>
-  <si>
-    <t>Caramel</t>
-  </si>
-  <si>
-    <t>co3</t>
-  </si>
-  <si>
-    <t>Fruit rouge</t>
-  </si>
-  <si>
-    <t>co4</t>
-  </si>
-  <si>
-    <t>co5</t>
-  </si>
-  <si>
-    <t>croquant</t>
-  </si>
-  <si>
-    <t>Croquant</t>
-  </si>
-  <si>
-    <t>cr1</t>
-  </si>
-  <si>
-    <t>M&amp;M's</t>
-  </si>
-  <si>
-    <t>cr2</t>
-  </si>
-  <si>
-    <t>Daim</t>
-  </si>
-  <si>
-    <t>cr3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speculos </t>
-  </si>
-  <si>
-    <t>cr4</t>
-  </si>
-  <si>
-    <t>Sans croquant</t>
-  </si>
-  <si>
-    <t>cr5</t>
-  </si>
-  <si>
-    <t>nappage_crepe</t>
-  </si>
-  <si>
-    <t>Nappage crêpe/gaufre</t>
-  </si>
-  <si>
-    <t>na1</t>
-  </si>
-  <si>
-    <t>Sucre</t>
-  </si>
-  <si>
-    <t>na2</t>
-  </si>
-  <si>
-    <t>Nature</t>
-  </si>
-  <si>
-    <t>na3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Citron frais </t>
-  </si>
-  <si>
-    <t>na4</t>
-  </si>
-  <si>
-    <t>Coulis chocolat</t>
-  </si>
-  <si>
-    <t>na5</t>
-  </si>
-  <si>
-    <t>Coulis caramel</t>
-  </si>
-  <si>
-    <t>na6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">glace vanille </t>
-  </si>
-  <si>
-    <t>sauce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sauce </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mariniére </t>
-  </si>
-  <si>
-    <t>Rocquefort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curry </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créme-échalote </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomate Chorizo </t>
-  </si>
-  <si>
-    <t>s0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pas de sauce </t>
+    <t>Grenadine</t>
+  </si>
+  <si>
+    <t>Cassis</t>
+  </si>
+  <si>
+    <t>Pêche</t>
+  </si>
+  <si>
+    <t>b41</t>
+  </si>
+  <si>
+    <t>Fraise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bieres </t>
+  </si>
+  <si>
+    <t>Bière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heineken </t>
+  </si>
+  <si>
+    <t>Blanche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desperados </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rouge </t>
   </si>
   <si>
     <t>💡 ID Famille identique sur plusieurs lignes = les options d'une même famille (ex: coulis)</t>
@@ -1146,6 +1233,9 @@
     <t>💡 Créez une nouvelle famille en inventant un nouvel ID Famille (ex: 'sauce_burger')</t>
   </si>
   <si>
+    <t xml:space="preserve">ICI ON RENTRE LES DECLINAISONS ET ON CHOISI LE NOM DE LA FAMILLE </t>
+  </si>
+  <si>
     <t>ASSIGNATION DES OPTIONS AUX PRODUITS</t>
   </si>
   <si>
@@ -1164,10 +1254,16 @@
     <t xml:space="preserve">Gaufre </t>
   </si>
   <si>
+    <t>bieres pression</t>
+  </si>
+  <si>
     <t>💡 Le Sundae a 2 lignes : coulis (étape 1) puis croquant (étape 2) → 2 popups successifs</t>
   </si>
   <si>
     <t>💡 Pour un produit sans option, ne créez simplement aucune ligne pour son ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ID PRODUIT = ID PRODUIT DE LA CARTE , ID FAMILLE = ID FAMILLE DANS FAMILLES OPTIONS </t>
   </si>
 </sst>
 </file>
@@ -2590,7 +2686,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2603,7 +2699,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2614,7 +2710,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2625,19 +2721,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>14</v>
@@ -2648,16 +2744,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E4" s="5">
         <v>0</v>
@@ -2671,16 +2767,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="E5" s="7">
         <v>0</v>
@@ -2694,16 +2790,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E6" s="5">
         <v>0</v>
@@ -2717,16 +2813,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E7" s="5">
         <v>0</v>
@@ -2740,16 +2836,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="E8" s="5">
         <v>0</v>
@@ -2763,16 +2859,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="E9" s="7">
         <v>0.5</v>
@@ -2786,16 +2882,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="E10" s="5">
         <v>0.5</v>
@@ -2809,16 +2905,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E11" s="7">
         <v>0.5</v>
@@ -2832,16 +2928,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E12" s="7">
         <v>0</v>
@@ -2855,16 +2951,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="4" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E13" s="7">
         <v>0</v>
@@ -2878,16 +2974,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="E14" s="5">
         <v>0</v>
@@ -2901,16 +2997,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>345</v>
+        <v>354</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="E15" s="7">
         <v>0</v>
@@ -2924,16 +3020,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="E16" s="5">
         <v>0</v>
@@ -2947,16 +3043,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>345</v>
+        <v>354</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="E17" s="7">
         <v>0</v>
@@ -2970,16 +3066,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>345</v>
+        <v>354</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E18" s="7">
         <v>0</v>
@@ -2993,19 +3089,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>345</v>
+        <v>354</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>355</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="E19" s="7">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F19" s="6" t="s">
         <v>62</v>
@@ -3016,16 +3112,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="E20" s="7">
         <v>0</v>
@@ -3039,16 +3135,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E21" s="7">
         <v>0</v>
@@ -3062,16 +3158,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="E22" s="7">
         <v>0</v>
@@ -3085,16 +3181,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="E23" s="7">
         <v>0</v>
@@ -3108,16 +3204,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="E24" s="7">
         <v>0</v>
@@ -3131,16 +3227,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E25" s="7">
         <v>0</v>
@@ -3154,16 +3250,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="E26" s="7">
         <v>0</v>
@@ -3175,14 +3271,345 @@
         <v>7</v>
       </c>
     </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G27" s="7">
+        <v>8</v>
+      </c>
+    </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="8" t="s">
-        <v>367</v>
+      <c r="A28" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G28" s="7">
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="8" t="s">
-        <v>368</v>
+      <c r="A29" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G29" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G31" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G32" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G33" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G34" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G36" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G37" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G38" s="7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="4"/>
+      <c r="B40" s="7"/>
+      <c r="C40" s="4"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="7"/>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="B46" t="s">
+        <v>398</v>
       </c>
     </row>
   </sheetData>
@@ -3194,7 +3621,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3206,7 +3633,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>369</v>
+        <v>399</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3215,7 +3642,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>370</v>
+        <v>400</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3224,16 +3651,16 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>371</v>
+        <v>401</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>372</v>
+        <v>402</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>373</v>
+        <v>403</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>14</v>
@@ -3241,13 +3668,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="D4" s="5">
         <v>1</v>
@@ -3258,16 +3685,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>240</v>
+        <v>244</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="D5" s="7">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="D5" s="5">
+        <v>2</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>62</v>
@@ -3275,16 +3702,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>374</v>
+        <v>249</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="D6" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>62</v>
@@ -3292,16 +3719,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>243</v>
+        <v>248</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>404</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D7" s="5">
-        <v>1</v>
+        <v>343</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>62</v>
@@ -3309,16 +3736,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>243</v>
+        <v>251</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>252</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="D8" s="7">
-        <v>2</v>
+      <c r="D8" s="5">
+        <v>1</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>62</v>
@@ -3326,29 +3753,147 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="7">
+        <v>2</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C10" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D10" s="7">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="8" t="s">
-        <v>375</v>
+      <c r="E10" s="6" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="8" t="s">
-        <v>376</v>
+      <c r="A11" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="4"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="4"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="4"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="6"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="4"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="8" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="8" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -3527,10 +4072,10 @@
         <v>72</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>70</v>
+        <v>73</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="G7" s="5">
         <v>15.9</v>
@@ -3544,7 +4089,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>58</v>
@@ -3553,13 +4098,13 @@
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G8" s="7">
         <v>0</v>
@@ -3573,7 +4118,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>58</v>
@@ -3582,13 +4127,13 @@
         <v>2</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G9" s="5">
         <v>15.9</v>
@@ -3602,7 +4147,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3629,7 +4174,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3642,7 +4187,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3684,22 +4229,22 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -3713,22 +4258,22 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G5" s="7">
         <v>0</v>
@@ -3742,22 +4287,22 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
@@ -3771,22 +4316,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G7" s="7">
         <v>0</v>
@@ -3800,22 +4345,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -3829,22 +4374,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G9" s="7">
         <v>0</v>
@@ -3856,9 +4401,36 @@
         <v>6</v>
       </c>
     </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G10" s="7">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I10" s="7">
+        <v>7</v>
+      </c>
+    </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -3885,7 +4457,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3898,7 +4470,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3940,7 +4512,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
@@ -3953,22 +4525,22 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G5" s="5">
         <v>2.5</v>
@@ -3982,22 +4554,22 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G6" s="7">
         <v>2.5</v>
@@ -4011,22 +4583,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G7" s="5">
         <v>2.5</v>
@@ -4040,22 +4612,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G8" s="7">
         <v>2</v>
@@ -4069,22 +4641,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="G9" s="5">
         <v>2</v>
@@ -4098,22 +4670,22 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G10" s="7">
         <v>4.5</v>
@@ -4127,7 +4699,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="10" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -4140,22 +4712,22 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G12" s="5">
         <v>3.5</v>
@@ -4169,22 +4741,22 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G13" s="7">
         <v>6</v>
@@ -4198,22 +4770,22 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G14" s="5">
         <v>4.5</v>
@@ -4227,22 +4799,22 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>142</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>137</v>
       </c>
       <c r="G15" s="7">
         <v>4</v>
@@ -4256,7 +4828,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="10" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -4269,22 +4841,22 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G17" s="5">
         <v>4.5</v>
@@ -4298,22 +4870,22 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B18" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="C18" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G18" s="7">
         <v>9.5</v>
@@ -4327,22 +4899,22 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="E19" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G19" s="5">
         <v>17</v>
@@ -4356,22 +4928,22 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>154</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>149</v>
       </c>
       <c r="G20" s="7">
         <v>19</v>
@@ -4385,22 +4957,22 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G21" s="5">
         <v>18</v>
@@ -4414,22 +4986,22 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G22" s="7">
         <v>32</v>
@@ -4443,7 +5015,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="10" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B23" s="10"/>
       <c r="C23" s="10"/>
@@ -4456,22 +5028,22 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G24" s="5">
         <v>4.5</v>
@@ -4485,22 +5057,22 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G25" s="7">
         <v>9.5</v>
@@ -4514,22 +5086,22 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G26" s="5">
         <v>16</v>
@@ -4543,22 +5115,22 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>162</v>
-      </c>
       <c r="D27" s="7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G27" s="7">
         <v>19</v>
@@ -4572,22 +5144,22 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F28" s="5" t="s">
         <v>169</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="G28" s="5">
         <v>20</v>
@@ -4601,22 +5173,22 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G29" s="7">
         <v>36</v>
@@ -4630,7 +5202,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -4643,22 +5215,22 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G31" s="5">
         <v>17</v>
@@ -4672,22 +5244,22 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G32" s="7">
         <v>16</v>
@@ -4701,7 +5273,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -4714,22 +5286,22 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="G34" s="5">
         <v>9</v>
@@ -4743,22 +5315,22 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G35" s="7">
         <v>9</v>
@@ -4772,22 +5344,22 @@
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="G36" s="5">
         <v>9</v>
@@ -4801,22 +5373,22 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="4" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="G37" s="7">
         <v>3</v>
@@ -4830,22 +5402,22 @@
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="4" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G38" s="5">
         <v>5.5</v>
@@ -4859,22 +5431,22 @@
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G39" s="7">
         <v>10</v>
@@ -4888,22 +5460,22 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G40" s="5">
         <v>16</v>
@@ -4917,7 +5489,7 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="10" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B41" s="10"/>
       <c r="C41" s="10"/>
@@ -4930,22 +5502,22 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G42" s="5">
         <v>1.5</v>
@@ -4959,22 +5531,22 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G43" s="7">
         <v>1.5</v>
@@ -4988,18 +5560,18 @@
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="4" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="E44" s="7"/>
       <c r="F44" s="7" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G44" s="7">
         <v>2</v>
@@ -5013,18 +5585,20 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E45" s="7"/>
+        <v>219</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>220</v>
+      </c>
       <c r="F45" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="G45" s="7">
         <v>2.5</v>
@@ -5038,19 +5612,23 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>203</v>
+        <v>118</v>
       </c>
       <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
+      <c r="D46" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>223</v>
+      </c>
       <c r="F46" s="7" t="s">
-        <v>212</v>
+        <v>131</v>
       </c>
       <c r="G46" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>62</v>
@@ -5061,16 +5639,16 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="4" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
       <c r="F47" s="7" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G47" s="7">
         <v>5</v>
@@ -5084,16 +5662,16 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="4" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
       <c r="F48" s="7" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G48" s="7">
         <v>6</v>
@@ -5107,16 +5685,16 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="4" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
       <c r="F49" s="7" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G49" s="7">
         <v>7</v>
@@ -5130,16 +5708,16 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="4" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
       <c r="F50" s="7" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="G50" s="7">
         <v>8</v>
@@ -5175,7 +5753,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5188,7 +5766,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5230,28 +5808,28 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="G4" s="5">
         <v>3.5</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="I4" s="5">
         <v>1</v>
@@ -5259,28 +5837,28 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="G5" s="7">
         <v>3.5</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="I5" s="7">
         <v>2</v>
@@ -5288,28 +5866,28 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="C6" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="G6" s="5">
         <v>3.5</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
       <c r="I6" s="5">
         <v>3</v>
@@ -5317,22 +5895,22 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="G7" s="7">
         <v>3.5</v>
@@ -5346,22 +5924,22 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="G8" s="5">
         <v>4.5</v>
@@ -5375,22 +5953,22 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="G9" s="7">
         <v>5.5</v>
@@ -5404,7 +5982,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5422,7 +6000,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
+    <col min="5" max="5" width="41.0973451327434" customWidth="1"/>
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
@@ -5431,7 +6009,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5444,7 +6022,7 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5486,22 +6064,22 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>122</v>
+        <v>260</v>
       </c>
       <c r="G4" s="5">
         <v>4.5</v>
@@ -5515,65 +6093,57 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>88</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="F5" s="7"/>
       <c r="G5" s="7">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I5" s="7">
-        <v>2</v>
-      </c>
+      <c r="I5" s="7"/>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="5">
-        <v>3</v>
-      </c>
+      <c r="I6" s="5"/>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="8" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -5597,7 +6167,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5606,7 +6176,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5632,16 +6202,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>62</v>
@@ -5649,16 +6219,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>62</v>
@@ -5666,16 +6236,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>62</v>
@@ -5683,16 +6253,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>62</v>
@@ -5700,16 +6270,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>62</v>
@@ -5717,16 +6287,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="4" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>62</v>
@@ -5734,16 +6304,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="4" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>131</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>62</v>
@@ -5751,33 +6321,33 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>62</v>
@@ -5785,16 +6355,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E13" s="6" t="s">
         <v>62</v>
@@ -5802,58 +6372,58 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" s="8" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -5877,7 +6447,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5886,7 +6456,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5912,16 +6482,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>62</v>
@@ -5929,16 +6499,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>62</v>
@@ -5946,16 +6516,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>62</v>
@@ -5963,41 +6533,41 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="8" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
     </row>
   </sheetData>
@@ -6021,7 +6591,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6030,7 +6600,7 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -6056,13 +6626,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="4" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>61</v>
@@ -6073,16 +6643,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>303</v>
+        <v>74</v>
       </c>
       <c r="E5" s="6" t="s">
         <v>62</v>
@@ -6090,16 +6660,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="4" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>62</v>
@@ -6107,41 +6677,41 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="4" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="4" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>62</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="8" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
     </row>
   </sheetData>
